--- a/Web crawling/Review/tags_by_store/S016.xlsx
+++ b/Web crawling/Review/tags_by_store/S016.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="카테고리태그" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,8 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,6 +418,14 @@
   </sheetPr>
   <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -449,1207 +460,1207 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>디저트가 맛있어요</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>3540</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="1" t="n">
+        <v>3551</v>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>맛</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>4128</v>
+      <c r="F2" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>음료가 맛있어요</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1733</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="1" t="n">
+        <v>1738</v>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>맛</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>4128</v>
+      <c r="F3" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>인테리어가 멋져요</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>1548</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="1" t="n">
+        <v>1552</v>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>인테리어</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>4128</v>
+      <c r="F4" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>커피가 맛있어요</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>1532</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="1" t="n">
+        <v>1536</v>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>맛</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>4128</v>
+      <c r="F5" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>특별한 메뉴가 있어요</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>1323</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="1" t="n">
+        <v>1325</v>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>메뉴</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>4128</v>
+      <c r="F6" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>친절해요</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>907</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="1" t="n">
+        <v>908</v>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>서비스</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>4128</v>
+      <c r="F7" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>사진이 잘 나와요</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>903</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="1" t="n">
+        <v>905</v>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>사진</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>4128</v>
+      <c r="F8" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>대화하기 좋아요</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>700</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="1" t="n">
+        <v>703</v>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>분위기</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>4128</v>
+      <c r="F9" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>매장이 청결해요</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>638</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="1" t="n">
+        <v>640</v>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>청결도</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>4128</v>
+      <c r="F10" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>매장이 넓어요</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="1" t="n">
         <v>243</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>공간</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>4128</v>
+      <c r="F11" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>음식이 맛있어요</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>198</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>맛</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>4128</v>
+      <c r="F12" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>뷰가 좋아요</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>160</v>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D13" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>전망</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>4128</v>
+      <c r="F13" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>가성비가 좋아요</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>4128</v>
+      <c r="F14" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>메뉴 구성이 알차요</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>105</v>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="D15" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>메뉴</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>4128</v>
+      <c r="F15" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>종류가 다양해요</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>메뉴</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>4128</v>
+      <c r="F16" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>빵이 맛있어요</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>맛</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>4128</v>
+      <c r="F17" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>아늑해요</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>분위기</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>4128</v>
+      <c r="F18" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>좌석이 편해요</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>편의</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>4128</v>
+      <c r="F19" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>비싼 만큼 가치있어요</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>4128</v>
+      <c r="F20" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>음악이 좋아요</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>분위기</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>4128</v>
+      <c r="F21" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>집중하기 좋아요</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>편의</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>4128</v>
+      <c r="F22" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>화장실이 깨끗해요</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>청결도</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>4128</v>
+      <c r="F23" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>차분한 분위기예요</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="1" t="inlineStr">
         <is>
           <t>분위기</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>4128</v>
+      <c r="F24" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>양이 많아요</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>음식량</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>4128</v>
+      <c r="F25" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>재료가 신선해요</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>맛</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>4128</v>
+      <c r="F26" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>건강한 맛이에요</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>맛</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>4128</v>
+      <c r="F27" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>컨셉이 독특해요</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="1" t="inlineStr">
         <is>
           <t>분위기</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>4128</v>
+      <c r="F28" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>단체모임 하기 좋아요</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>17</v>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D29" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
         <is>
           <t>분위기</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>4128</v>
+      <c r="F29" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>특별한 날 가기 좋아요</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>15</v>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D30" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>목적</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>4128</v>
+      <c r="F30" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>음식이 빨리 나와요</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>서비스</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>4128</v>
+      <c r="F31" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>오래 머무르기 좋아요</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>분위기</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>4128</v>
+      <c r="F32" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>아이와 가기 좋아요</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="1" t="inlineStr">
         <is>
           <t>목적</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>4128</v>
+      <c r="F33" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>주차하기 편해요</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="1" t="inlineStr">
         <is>
           <t>편의</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>4128</v>
+      <c r="F34" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>혼밥하기 좋아요</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="1" t="inlineStr">
         <is>
           <t>목적</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>4128</v>
+      <c r="F35" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>반려동물과 가기 좋아요</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="1" t="inlineStr">
         <is>
           <t>편의</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>4128</v>
+      <c r="F36" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>주문제작을 잘해줘요</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>서비스</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>4128</v>
+      <c r="F37" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>야외공간이 멋져요</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>전망</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>4128</v>
+      <c r="F38" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>룸이 잘 되어있어요</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="1" t="inlineStr">
         <is>
           <t>인테리어</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>4128</v>
+      <c r="F39" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>선물하기 좋아요</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="1" t="inlineStr">
         <is>
           <t>목적</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>4128</v>
+      <c r="F40" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>파티하기 좋아요</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="1" t="inlineStr">
         <is>
           <t>목적</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>4128</v>
+      <c r="F41" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>차가 맛있어요</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="1" t="inlineStr">
         <is>
           <t>맛</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>4128</v>
+      <c r="F42" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>술이 다양해요</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="1" t="inlineStr">
         <is>
           <t>메뉴</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>4128</v>
+      <c r="F43" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>S016</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>라헬의부엌 홍대점</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>라헬의부엌 홍대점</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>읽을만한 책이 많아요</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>편의</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>4128</v>
+      <c r="F44" s="1" t="n">
+        <v>4139</v>
       </c>
     </row>
   </sheetData>
